--- a/public/Tabela final atualizada .xlsx
+++ b/public/Tabela final atualizada .xlsx
@@ -1473,7 +1473,7 @@
         <v>Retatrutida 120mg Mixed</v>
       </c>
       <c r="D84" t="str">
-        <v>5 Bujões de 24mg + 1 Água</v>
+        <v>2 bujões de 60mg Aquoso</v>
       </c>
       <c r="E84" s="1">
         <v>2990</v>
